--- a/research/elicitation/Directorate_Elicitation_Workbook.xlsx
+++ b/research/elicitation/Directorate_Elicitation_Workbook.xlsx
@@ -34,7 +34,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Rules!$A$4:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Symptoms!$A$4:$E$20</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -111,7 +111,7 @@
     <t>Scale of the model</t>
   </si>
   <si>
-    <t>25 causes in four provisional categories (application and interface; authentication and access; database; infrastructure and external services; please correct them), 20 checks, 10 rules (agreed scope). The number of symptoms and context attributes is open; 15 symptom rows and 6 context rows are provided.</t>
+    <t>About 15 causes (more if they can be described well; rows are provided for up to 25) in four provisional categories (application and interface; authentication and access; database; infrastructure and external services; please correct them), 20 checks, 10 rules (agreed scope). The number of symptoms and context attributes is open; 15 symptom rows and 6 context rows are provided.</t>
   </si>
   <si>
     <t>Recording sources</t>
@@ -279,7 +279,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>1. Causes and remedies (25)</t>
+    <t>1. Causes and remedies (about 15; rows for up to 25)</t>
   </si>
   <si>
     <t>One row per cause. Each cause has exactly one remedy: the action that resolves an incident with that cause.</t>
@@ -6165,11 +6165,11 @@
         <v>0</v>
       </c>
       <c r="C5" s="12">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D5" s="13">
         <f t="shared" ref="D5:D15" si="0">IF(ISNUMBER(C5),MAX(C5-B5,0),"")</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -6181,11 +6181,11 @@
         <v>0</v>
       </c>
       <c r="C6" s="12">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
@@ -6197,11 +6197,11 @@
         <v>0</v>
       </c>
       <c r="C7" s="12">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D7" s="13">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
@@ -6213,11 +6213,11 @@
         <v>0</v>
       </c>
       <c r="C8" s="12">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D8" s="13">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
@@ -6293,11 +6293,12 @@
         <v>0</v>
       </c>
       <c r="C13" s="12">
-        <v>500</v>
+        <f>MAX(15,B5)*20</f>
+        <v>300</v>
       </c>
       <c r="D13" s="13">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
@@ -6309,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="12">
-        <f>B11*25</f>
+        <f>B11*MAX(15,B5)</f>
         <v>0</v>
       </c>
       <c r="D14" s="13">
